--- a/变电站/2026年7月/收据/408房_7月收据.xlsx
+++ b/变电站/2026年7月/收据/408房_7月收据.xlsx
@@ -690,7 +690,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
@@ -719,7 +719,7 @@
         <v>46</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
